--- a/GBDS MAY FILES 2026/DSSR GBDS MONTH OF MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/DSSR GBDS MONTH OF MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7A327A-BBD6-491B-8213-622434D1983E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15CFAD7-B95A-4E95-9996-889689B0B14A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
